--- a/output/pdf_financials_xlsx/CAMB.xlsx
+++ b/output/pdf_financials_xlsx/CAMB.xlsx
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.174</v>
+        <v>-0.174</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.981</v>
+        <v>-0.981</v>
       </c>
     </row>
     <row r="18">
@@ -3324,7 +3324,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>-0.174</v>
       </c>
@@ -3664,7 +3668,11 @@
           <t>Proceeds from share issuance 14</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>109.352</v>
       </c>
@@ -4526,7 +4534,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
         <v>0.174</v>
       </c>
